--- a/InputData/indst/IFTQfEERP/Indst Fuel Types Qual for Early Eqpt Retirement Policy.xlsx
+++ b/InputData/indst/IFTQfEERP/Indst Fuel Types Qual for Early Eqpt Retirement Policy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\IFTQfEERP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\IFTQfEERP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F5B5DD-72D6-4130-9F6F-DB3C04594B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A667F574-D0AA-4EB0-8B3F-139EA5594795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32670" yWindow="2055" windowWidth="21405" windowHeight="13005" xr2:uid="{05F795DA-2DEA-4188-AD09-B14B246EEF5D}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" xr2:uid="{05F795DA-2DEA-4188-AD09-B14B246EEF5D}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Source:</t>
   </si>
@@ -79,12 +79,6 @@
   </si>
   <si>
     <t>Unit: dimensionless</t>
-  </si>
-  <si>
-    <t>green hydrogen if</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen if</t>
   </si>
   <si>
     <t>IFTQfEERP Industrial Fuel Types Qualifying for Early Equipment Retirement Policy</t>
@@ -160,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -172,8 +166,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -516,7 +508,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -524,7 +516,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -537,32 +529,32 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>21</v>
+      <c r="A12" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>19</v>
+      <c r="A13" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -576,7 +568,7 @@
   <sheetPr>
     <tabColor theme="3" tint="9.9978637043366805E-2"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.5703125" customWidth="1"/>
@@ -594,7 +586,7 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2">
         <v>0</v>
       </c>
     </row>
@@ -602,7 +594,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3">
         <v>1</v>
       </c>
     </row>
@@ -610,7 +602,7 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -618,7 +610,7 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <v>1</v>
       </c>
     </row>
@@ -626,7 +618,7 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6">
         <v>1</v>
       </c>
     </row>
@@ -634,7 +626,7 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <v>0</v>
       </c>
     </row>
@@ -642,7 +634,7 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8">
         <v>1</v>
       </c>
     </row>
@@ -650,7 +642,7 @@
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9">
         <v>1</v>
       </c>
     </row>
@@ -658,7 +650,7 @@
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10">
         <v>1</v>
       </c>
     </row>
@@ -666,23 +658,7 @@
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="6">
+      <c r="B11">
         <v>0</v>
       </c>
     </row>
